--- a/ds/3des/03-pdm1/aula08/testes.xlsx
+++ b/ds/3des/03-pdm1/aula08/testes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\03-pdm1\aula08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21F6CD84-0431-45EB-939B-625041BBCC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C682332-D19F-482F-B5D1-BB6785FB9B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CB4A1E4E-B4C8-4F78-B91F-00749332879B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>C</t>
   </si>
@@ -57,13 +57,41 @@
   </si>
   <si>
     <t>outras</t>
+  </si>
+  <si>
+    <t>Financiamentos</t>
+  </si>
+  <si>
+    <t>Investimentos</t>
+  </si>
+  <si>
+    <t>Mensalidade</t>
+  </si>
+  <si>
+    <t>Mêses</t>
+  </si>
+  <si>
+    <t>Taxa de juros</t>
+  </si>
+  <si>
+    <t>Sem juros</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,14 +117,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -429,63 +461,710 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2914069F-8676-4979-B4DA-9E99B6AF8EFE}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1">
+        <v>1</v>
+      </c>
+      <c r="H1" s="3">
+        <f>$E$2</f>
+        <v>200</v>
+      </c>
+      <c r="I1" s="3">
+        <f>H1*$E$4</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
+      <c r="B2" s="2">
         <v>50000</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2">
+        <v>200</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2" s="3">
+        <f>H1+I1+$E$2</f>
+        <v>402</v>
+      </c>
+      <c r="I2" s="3">
+        <f t="shared" ref="I2:I48" si="0">H2*$E$4</f>
+        <v>4.0200000000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B3" s="1">
         <v>7.4999999999999997E-3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>48</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3" s="3">
+        <f>H2+I2+$E$2</f>
+        <v>606.02</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0602</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3">
+        <f t="shared" ref="H3:H26" si="1">H3+I3+$E$2</f>
+        <v>812.08019999999999</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>8.1208019999999994</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B5" s="2">
         <v>500</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3">
+        <f>E2*E3</f>
+        <v>9600</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5" s="3">
+        <f>H4+I4+$E$2</f>
+        <v>1020.201002</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>10.202010020000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6" s="3">
+        <f t="shared" si="1"/>
+        <v>1230.40301202</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>12.3040301202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
-        <f>B1*(1+B2)^B3 + B4</f>
+      <c r="B7" s="2">
+        <f>B2*(1+B3)^B4 + B5</f>
         <v>72070.266665685616</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7" s="3">
+        <f t="shared" si="1"/>
+        <v>1442.7070421402</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>14.427070421402</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="B7">
-        <f>B6/B3</f>
+      <c r="B8" s="2">
+        <f>B7/B4</f>
         <v>1501.4638888684503</v>
       </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3">
+        <f t="shared" si="1"/>
+        <v>1657.134112561602</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>16.571341125616019</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9" s="3">
+        <f t="shared" si="1"/>
+        <v>1873.7054536872181</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>18.737054536872183</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10" s="3">
+        <f t="shared" si="1"/>
+        <v>2092.4425082240905</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>20.924425082240905</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G11">
+        <v>11</v>
+      </c>
+      <c r="H11" s="3">
+        <f t="shared" si="1"/>
+        <v>2313.3669333063312</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="0"/>
+        <v>23.133669333063313</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G12">
+        <v>12</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" si="1"/>
+        <v>2536.5006026393944</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="0"/>
+        <v>25.365006026393946</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G13">
+        <v>13</v>
+      </c>
+      <c r="H13" s="3">
+        <f t="shared" si="1"/>
+        <v>2761.8656086657884</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>27.618656086657886</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G14">
+        <v>14</v>
+      </c>
+      <c r="H14" s="3">
+        <f t="shared" si="1"/>
+        <v>2989.4842647524461</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="0"/>
+        <v>29.89484264752446</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G15">
+        <v>15</v>
+      </c>
+      <c r="H15" s="3">
+        <f t="shared" si="1"/>
+        <v>3219.3791073999705</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="0"/>
+        <v>32.193791073999705</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G16">
+        <v>16</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" si="1"/>
+        <v>3451.5728984739703</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>34.515728984739702</v>
+      </c>
+    </row>
+    <row r="17" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G17">
+        <v>17</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" si="1"/>
+        <v>3686.0886274587101</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>36.860886274587102</v>
+      </c>
+    </row>
+    <row r="18" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G18">
+        <v>18</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" si="1"/>
+        <v>3922.9495137332974</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="0"/>
+        <v>39.229495137332975</v>
+      </c>
+    </row>
+    <row r="19" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G19">
+        <v>19</v>
+      </c>
+      <c r="H19" s="3">
+        <f t="shared" si="1"/>
+        <v>4162.1790088706302</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="0"/>
+        <v>41.621790088706305</v>
+      </c>
+    </row>
+    <row r="20" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G20">
+        <v>20</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" si="1"/>
+        <v>4403.8007989593361</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>44.03800798959336</v>
+      </c>
+    </row>
+    <row r="21" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G21">
+        <v>21</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" si="1"/>
+        <v>4647.8388069489292</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="0"/>
+        <v>46.478388069489291</v>
+      </c>
+    </row>
+    <row r="22" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G22">
+        <v>22</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" si="1"/>
+        <v>4894.3171950184187</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="0"/>
+        <v>48.943171950184187</v>
+      </c>
+    </row>
+    <row r="23" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G23">
+        <v>23</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" si="1"/>
+        <v>5143.2603669686032</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="0"/>
+        <v>51.432603669686031</v>
+      </c>
+    </row>
+    <row r="24" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G24">
+        <v>24</v>
+      </c>
+      <c r="H24" s="3">
+        <f t="shared" si="1"/>
+        <v>5394.6929706382889</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="0"/>
+        <v>53.946929706382889</v>
+      </c>
+    </row>
+    <row r="25" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G25">
+        <v>25</v>
+      </c>
+      <c r="H25" s="3">
+        <f t="shared" si="1"/>
+        <v>5648.6399003446713</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>56.486399003446714</v>
+      </c>
+    </row>
+    <row r="26" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G26">
+        <v>26</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" si="1"/>
+        <v>5905.1262993481178</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="0"/>
+        <v>59.051262993481181</v>
+      </c>
+    </row>
+    <row r="27" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G27">
+        <v>27</v>
+      </c>
+      <c r="H27" s="3">
+        <f t="shared" ref="H27:H48" si="2">H26+I26+$E$2</f>
+        <v>6164.1775623415988</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>61.641775623415988</v>
+      </c>
+    </row>
+    <row r="28" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G28">
+        <v>28</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" si="2"/>
+        <v>6425.8193379650147</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>64.258193379650152</v>
+      </c>
+    </row>
+    <row r="29" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G29">
+        <v>29</v>
+      </c>
+      <c r="H29" s="3">
+        <f t="shared" si="2"/>
+        <v>6690.0775313446647</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="0"/>
+        <v>66.900775313446644</v>
+      </c>
+    </row>
+    <row r="30" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G30">
+        <v>30</v>
+      </c>
+      <c r="H30" s="3">
+        <f t="shared" si="2"/>
+        <v>6956.9783066581113</v>
+      </c>
+      <c r="I30" s="3">
+        <f t="shared" si="0"/>
+        <v>69.56978306658111</v>
+      </c>
+    </row>
+    <row r="31" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G31">
+        <v>31</v>
+      </c>
+      <c r="H31" s="3">
+        <f t="shared" si="2"/>
+        <v>7226.5480897246925</v>
+      </c>
+      <c r="I31" s="3">
+        <f t="shared" si="0"/>
+        <v>72.265480897246931</v>
+      </c>
+    </row>
+    <row r="32" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G32">
+        <v>32</v>
+      </c>
+      <c r="H32" s="3">
+        <f t="shared" si="2"/>
+        <v>7498.8135706219391</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="0"/>
+        <v>74.988135706219396</v>
+      </c>
+    </row>
+    <row r="33" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G33">
+        <v>33</v>
+      </c>
+      <c r="H33" s="3">
+        <f t="shared" si="2"/>
+        <v>7773.8017063281586</v>
+      </c>
+      <c r="I33" s="3">
+        <f t="shared" si="0"/>
+        <v>77.738017063281589</v>
+      </c>
+    </row>
+    <row r="34" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G34">
+        <v>34</v>
+      </c>
+      <c r="H34" s="3">
+        <f t="shared" si="2"/>
+        <v>8051.53972339144</v>
+      </c>
+      <c r="I34" s="3">
+        <f t="shared" si="0"/>
+        <v>80.515397233914399</v>
+      </c>
+    </row>
+    <row r="35" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G35">
+        <v>35</v>
+      </c>
+      <c r="H35" s="3">
+        <f t="shared" si="2"/>
+        <v>8332.0551206253549</v>
+      </c>
+      <c r="I35" s="3">
+        <f t="shared" si="0"/>
+        <v>83.320551206253555</v>
+      </c>
+    </row>
+    <row r="36" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G36">
+        <v>36</v>
+      </c>
+      <c r="H36" s="3">
+        <f t="shared" si="2"/>
+        <v>8615.375671831609</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="0"/>
+        <v>86.153756718316089</v>
+      </c>
+    </row>
+    <row r="37" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G37">
+        <v>37</v>
+      </c>
+      <c r="H37" s="3">
+        <f t="shared" si="2"/>
+        <v>8901.5294285499258</v>
+      </c>
+      <c r="I37" s="3">
+        <f t="shared" si="0"/>
+        <v>89.015294285499266</v>
+      </c>
+    </row>
+    <row r="38" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G38">
+        <v>38</v>
+      </c>
+      <c r="H38" s="3">
+        <f t="shared" si="2"/>
+        <v>9190.5447228354242</v>
+      </c>
+      <c r="I38" s="3">
+        <f t="shared" si="0"/>
+        <v>91.905447228354248</v>
+      </c>
+    </row>
+    <row r="39" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G39">
+        <v>39</v>
+      </c>
+      <c r="H39" s="3">
+        <f t="shared" si="2"/>
+        <v>9482.4501700637793</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="0"/>
+        <v>94.824501700637796</v>
+      </c>
+    </row>
+    <row r="40" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G40">
+        <v>40</v>
+      </c>
+      <c r="H40" s="3">
+        <f t="shared" si="2"/>
+        <v>9777.2746717644168</v>
+      </c>
+      <c r="I40" s="3">
+        <f t="shared" si="0"/>
+        <v>97.772746717644168</v>
+      </c>
+    </row>
+    <row r="41" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G41">
+        <v>41</v>
+      </c>
+      <c r="H41" s="3">
+        <f t="shared" si="2"/>
+        <v>10075.047418482061</v>
+      </c>
+      <c r="I41" s="3">
+        <f t="shared" si="0"/>
+        <v>100.75047418482062</v>
+      </c>
+    </row>
+    <row r="42" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G42">
+        <v>42</v>
+      </c>
+      <c r="H42" s="3">
+        <f t="shared" si="2"/>
+        <v>10375.797892666882</v>
+      </c>
+      <c r="I42" s="3">
+        <f t="shared" si="0"/>
+        <v>103.75797892666883</v>
+      </c>
+    </row>
+    <row r="43" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G43">
+        <v>43</v>
+      </c>
+      <c r="H43" s="3">
+        <f t="shared" si="2"/>
+        <v>10679.555871593551</v>
+      </c>
+      <c r="I43" s="3">
+        <f t="shared" si="0"/>
+        <v>106.79555871593551</v>
+      </c>
+    </row>
+    <row r="44" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G44">
+        <v>44</v>
+      </c>
+      <c r="H44" s="3">
+        <f t="shared" si="2"/>
+        <v>10986.351430309487</v>
+      </c>
+      <c r="I44" s="3">
+        <f t="shared" si="0"/>
+        <v>109.86351430309487</v>
+      </c>
+    </row>
+    <row r="45" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G45">
+        <v>45</v>
+      </c>
+      <c r="H45" s="3">
+        <f t="shared" si="2"/>
+        <v>11296.214944612582</v>
+      </c>
+      <c r="I45" s="3">
+        <f t="shared" si="0"/>
+        <v>112.96214944612582</v>
+      </c>
+    </row>
+    <row r="46" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G46">
+        <v>46</v>
+      </c>
+      <c r="H46" s="3">
+        <f t="shared" si="2"/>
+        <v>11609.177094058708</v>
+      </c>
+      <c r="I46" s="3">
+        <f t="shared" si="0"/>
+        <v>116.09177094058708</v>
+      </c>
+    </row>
+    <row r="47" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G47">
+        <v>47</v>
+      </c>
+      <c r="H47" s="3">
+        <f t="shared" si="2"/>
+        <v>11925.268864999296</v>
+      </c>
+      <c r="I47" s="3">
+        <f t="shared" si="0"/>
+        <v>119.25268864999296</v>
+      </c>
+    </row>
+    <row r="48" spans="7:9" x14ac:dyDescent="0.25">
+      <c r="G48">
+        <v>48</v>
+      </c>
+      <c r="H48" s="3">
+        <f t="shared" si="2"/>
+        <v>12244.521553649289</v>
+      </c>
+      <c r="I48" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/3des/03-pdm1/aula08/testes.xlsx
+++ b/ds/3des/03-pdm1/aula08/testes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\03-pdm1\aula08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C682332-D19F-482F-B5D1-BB6785FB9B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E0AA0A-50FE-43AA-B044-CC8395DC866D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CB4A1E4E-B4C8-4F78-B91F-00749332879B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>C</t>
   </si>
@@ -75,14 +75,33 @@
   </si>
   <si>
     <t>Sem juros</t>
+  </si>
+  <si>
+    <t>disatancia</t>
+  </si>
+  <si>
+    <t>corrente</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>bitola 110</t>
+  </si>
+  <si>
+    <t>bitola 220</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -117,19 +136,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Vírgula" xfId="2" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -461,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2914069F-8676-4979-B4DA-9E99B6AF8EFE}">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
@@ -471,9 +493,11 @@
     <col min="7" max="7" width="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -491,8 +515,17 @@
         <f>H1*$E$4</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1">
+        <v>50</v>
+      </c>
+      <c r="M1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -513,11 +546,20 @@
         <v>402</v>
       </c>
       <c r="I2" s="3">
-        <f t="shared" ref="I2:I48" si="0">H2*$E$4</f>
+        <f t="shared" ref="I2:I47" si="0">H2*$E$4</f>
         <v>4.0200000000000005</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2">
+        <v>30</v>
+      </c>
+      <c r="M2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -541,8 +583,15 @@
         <f t="shared" si="0"/>
         <v>6.0602</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="4">
+        <f xml:space="preserve"> (2*L2*L1)/294.64</f>
+        <v>10.18191691555797</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -559,15 +608,22 @@
         <v>4</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" ref="H3:H26" si="1">H3+I3+$E$2</f>
+        <f t="shared" ref="H4:H26" si="1">H3+I3+$E$2</f>
         <v>812.08019999999999</v>
       </c>
       <c r="I4" s="3">
         <f t="shared" si="0"/>
         <v>8.1208019999999994</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="4">
+        <f xml:space="preserve"> (2*L2*L1)/510.4</f>
+        <v>5.8777429467084641</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -593,7 +649,7 @@
         <v>10.202010020000001</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -609,7 +665,7 @@
         <v>12.3040301202</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -629,7 +685,7 @@
         <v>14.427070421402</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -649,7 +705,7 @@
         <v>16.571341125616019</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G9">
         <v>9</v>
       </c>
@@ -662,7 +718,7 @@
         <v>18.737054536872183</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G10">
         <v>10</v>
       </c>
@@ -675,7 +731,7 @@
         <v>20.924425082240905</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G11">
         <v>11</v>
       </c>
@@ -688,7 +744,7 @@
         <v>23.133669333063313</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G12">
         <v>12</v>
       </c>
@@ -701,7 +757,7 @@
         <v>25.365006026393946</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G13">
         <v>13</v>
       </c>
@@ -714,7 +770,7 @@
         <v>27.618656086657886</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G14">
         <v>14</v>
       </c>
@@ -727,7 +783,7 @@
         <v>29.89484264752446</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G15">
         <v>15</v>
       </c>
@@ -740,7 +796,7 @@
         <v>32.193791073999705</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G16">
         <v>16</v>
       </c>
